--- a/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T12:51:02+00:00</t>
+    <t>2026-06-29T13:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T13:58:40+00:00</t>
+    <t>2026-06-29T14:49:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-smokingstatus-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:49:16+00:00</t>
+    <t>2026-06-29T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
